--- a/templates/sk/pl.xlsx
+++ b/templates/sk/pl.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6550"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="PL" sheetId="53286" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>GUANGDONG GLOBALSINO OUTDOOR SPORTS EQUIPMENT LIMITED</t>
   </si>
@@ -41,27 +41,19 @@
     <t>PACKING LIST</t>
   </si>
   <si>
+    <t>SHIPPING MARK:</t>
+  </si>
+  <si>
     <t xml:space="preserve">C/T#:                    </t>
   </si>
   <si>
     <t>Invoice No.</t>
   </si>
   <si>
-    <r>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发票号</t>
-    </r>
+    <t>MADE IN CHINA</t>
   </si>
   <si>
-    <t>MADE IN CHINA</t>
+    <t>Invoice Date.</t>
   </si>
   <si>
     <t>SAP PO#</t>
@@ -88,94 +80,10 @@
     <t>CTNS</t>
   </si>
   <si>
-    <t>括号内数值手动更新</t>
-  </si>
-  <si>
     <t>FISHING REELS (1277PCS,1001.21KGS)</t>
   </si>
   <si>
-    <r>
-      <t>RO new PO template A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Purchasing Document"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>RO new PO template J</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Model"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>RO new PO template I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Material"</t>
-    </r>
-  </si>
-  <si>
-    <t>PO record</t>
-  </si>
-  <si>
-    <t>SK+YM箱单</t>
-  </si>
-  <si>
-    <t>CB2500.B2</t>
-  </si>
-  <si>
-    <t>21-44640</t>
+    <t>TOTAL:</t>
   </si>
   <si>
     <t>PCS</t>
@@ -187,40 +95,10 @@
     <t>CBM</t>
   </si>
   <si>
-    <t>CB3000.B2</t>
-  </si>
-  <si>
-    <t>21-44641</t>
-  </si>
-  <si>
-    <t>CB4000.B2</t>
-  </si>
-  <si>
-    <t>21-44642</t>
-  </si>
-  <si>
-    <t>CB6000.B2</t>
-  </si>
-  <si>
-    <t>21-44644</t>
-  </si>
-  <si>
-    <t>CB8000.B2</t>
-  </si>
-  <si>
-    <t>21-44645</t>
-  </si>
-  <si>
-    <t>TOTAL:</t>
-  </si>
-  <si>
     <t>ORIGIN IN CHINA</t>
   </si>
   <si>
     <t>PACKED IN 88 CTNS</t>
-  </si>
-  <si>
-    <t>箱数手动更新</t>
   </si>
   <si>
     <t>THERE IS NO SOLID WOOD PACKING MATERIAL IN THIS SHIPMENT.</t>
@@ -248,7 +126,7 @@
     <numFmt numFmtId="186" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="187" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="78">
+  <fonts count="77">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -290,30 +168,26 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF00B0F0"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
@@ -326,14 +200,12 @@
       <b/>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF00B0F0"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
@@ -757,12 +629,6 @@
       <sz val="10"/>
       <name val="굴림체"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="40"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="59">
@@ -2100,7 +1966,7 @@
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="186" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2138,77 +2004,80 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="266" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="266" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="182" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="183" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="185" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2220,60 +2089,51 @@
     <xf numFmtId="184" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="183" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="267">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2841,20 +2701,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:CC29"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="4.83636363636364" style="6" customWidth="1"/>
-    <col min="2" max="2" width="15.4545454545455" style="6" customWidth="1"/>
-    <col min="3" max="3" width="11.8363636363636" style="6" customWidth="1"/>
+    <col min="1" max="1" width="4.83928571428571" style="6" customWidth="1"/>
+    <col min="2" max="2" width="15.4553571428571" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11.8392857142857" style="6" customWidth="1"/>
     <col min="4" max="4" width="9.5" style="6" customWidth="1"/>
     <col min="5" max="5" width="25.5" style="6" customWidth="1"/>
-    <col min="6" max="6" width="9.33636363636364" style="6" customWidth="1"/>
-    <col min="7" max="7" width="11.0909090909091" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.33928571428571" style="6" customWidth="1"/>
+    <col min="7" max="7" width="11.0892857142857" style="6" customWidth="1"/>
     <col min="8" max="8" width="9" style="6" customWidth="1"/>
-    <col min="9" max="9" width="8.33636363636364" style="6" customWidth="1"/>
-    <col min="10" max="10" width="7.33636363636364" style="7" customWidth="1"/>
-    <col min="11" max="12" width="5.66363636363636" style="7" customWidth="1"/>
-    <col min="13" max="13" width="11.4545454545455" style="8" customWidth="1"/>
+    <col min="9" max="9" width="8.33928571428571" style="6" customWidth="1"/>
+    <col min="10" max="10" width="7.33928571428571" style="7" customWidth="1"/>
+    <col min="11" max="12" width="5.66071428571429" style="7" customWidth="1"/>
+    <col min="13" max="13" width="11.4553571428571" style="8" customWidth="1"/>
     <col min="14" max="16384" width="12" style="6"/>
   </cols>
   <sheetData>
@@ -2925,10 +2785,12 @@
       <c r="M4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
-      <c r="A5" s="12"/>
+      <c r="A5" s="12" t="s">
+        <v>3</v>
+      </c>
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="16"/>
@@ -2937,425 +2799,232 @@
       <c r="H5" s="18"/>
       <c r="I5" s="17"/>
       <c r="J5" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="67" t="s">
         <v>5</v>
       </c>
+      <c r="K5" s="20"/>
       <c r="L5" s="20"/>
       <c r="M5" s="21"/>
     </row>
     <row r="6" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
-      <c r="A6" s="12"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
-      <c r="F6" s="12"/>
+      <c r="F6" s="22"/>
       <c r="G6" s="17"/>
       <c r="H6" s="18"/>
       <c r="I6" s="17"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="23"/>
+      <c r="J6" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="23"/>
+      <c r="L6" s="24"/>
       <c r="M6" s="21"/>
     </row>
     <row r="7" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
-      <c r="A7" s="12"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="13"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="27"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="28"/>
       <c r="I7" s="21"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="27"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="21"/>
     </row>
     <row r="8" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="28" t="s">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="C8" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="D8" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31" t="s">
+      <c r="E8" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="31"/>
-      <c r="I8" s="32" t="s">
+      <c r="F8" s="31"/>
+      <c r="G8" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32" t="s">
+      <c r="H8" s="32"/>
+      <c r="I8" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="33"/>
       <c r="M8" s="21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A9" s="21"/>
       <c r="B9" s="16"/>
-      <c r="C9" s="33" t="s">
-        <v>15</v>
-      </c>
+      <c r="C9" s="34"/>
       <c r="D9" s="21"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="27"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
       <c r="I9" s="21"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="27"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="21"/>
     </row>
     <row r="10" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A10" s="21"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36" t="s">
+      <c r="B10" s="36"/>
+      <c r="C10" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="39"/>
       <c r="M10" s="21"/>
     </row>
     <row r="11" s="3" customFormat="1" ht="53" customHeight="1" spans="1:14">
       <c r="A11" s="21"/>
-      <c r="B11" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="38"/>
-      <c r="G11" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="43"/>
-      <c r="K11" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="42" t="s">
-        <v>21</v>
-      </c>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="43"/>
     </row>
     <row r="12" s="3" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A12" s="21"/>
-      <c r="B12" s="35">
-        <v>4500028983</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="44">
-        <v>96</v>
-      </c>
-      <c r="F12" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="39">
-        <f>38.59+3</f>
-        <v>41.59</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="40">
-        <f>45.4+3.3</f>
-        <v>48.7</v>
-      </c>
-      <c r="J12" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="40">
-        <v>0.31</v>
-      </c>
-      <c r="L12" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" s="44">
-        <v>6</v>
-      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="41"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
     </row>
     <row r="13" s="4" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A13" s="21"/>
-      <c r="B13" s="35">
-        <v>4500028983</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="44">
-        <v>262</v>
-      </c>
-      <c r="F13" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="39">
-        <v>117.67</v>
-      </c>
-      <c r="H13" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="39">
-        <v>138.43</v>
-      </c>
-      <c r="J13" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="40">
-        <v>0.78</v>
-      </c>
-      <c r="L13" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="44">
-        <v>15</v>
-      </c>
+      <c r="B13" s="36"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
       <c r="N13" s="3"/>
     </row>
     <row r="14" s="4" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A14" s="21"/>
-      <c r="B14" s="35">
-        <v>4500028983</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="44">
-        <v>292</v>
-      </c>
-      <c r="F14" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="39">
-        <f>136.41+2.01</f>
-        <v>138.42</v>
-      </c>
-      <c r="H14" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="39">
-        <f>160.48+2.6</f>
-        <v>163.08</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="40">
-        <v>0.83</v>
-      </c>
-      <c r="L14" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="44">
-        <v>16</v>
-      </c>
+      <c r="B14" s="36"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
       <c r="N14" s="3"/>
     </row>
     <row r="15" s="4" customFormat="1" ht="16" customHeight="1" spans="1:14">
       <c r="A15" s="21"/>
-      <c r="B15" s="35">
-        <v>4500028983</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="44">
-        <v>132</v>
-      </c>
-      <c r="F15" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="39">
-        <v>101.35</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="39">
-        <v>119.24</v>
-      </c>
-      <c r="J15" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="40">
-        <v>0.58</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="44">
-        <v>11</v>
-      </c>
+      <c r="B15" s="36"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
       <c r="N15" s="3"/>
     </row>
     <row r="16" s="4" customFormat="1" ht="16" customHeight="1" spans="1:14">
-      <c r="A16" s="45"/>
-      <c r="B16" s="35">
-        <v>4500028983</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="44">
-        <v>425</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="39">
-        <f>245.62+175.44</f>
-        <v>421.06</v>
-      </c>
-      <c r="H16" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" s="40">
-        <f>288.96+206.4</f>
-        <v>495.36</v>
-      </c>
-      <c r="J16" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="40">
-        <f>1.55+1.11</f>
-        <v>2.66</v>
-      </c>
-      <c r="L16" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" s="44">
-        <v>36</v>
-      </c>
+      <c r="A16" s="21"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
       <c r="N16" s="3"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="16" customHeight="1" spans="1:81">
       <c r="A17" s="21"/>
-      <c r="B17" s="35">
-        <v>4500030322</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="44">
-        <v>16</v>
-      </c>
-      <c r="F17" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="39">
-        <v>6.77</v>
-      </c>
-      <c r="H17" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="39">
-        <v>7.96</v>
-      </c>
-      <c r="J17" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="40">
-        <v>0.05</v>
-      </c>
-      <c r="L17" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" s="44">
-        <v>1</v>
-      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
     </row>
     <row r="18" s="3" customFormat="1" ht="16" customHeight="1" spans="1:81">
-      <c r="A18" s="45"/>
-      <c r="B18" s="35">
-        <v>4500030322</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="44">
-        <v>54</v>
-      </c>
-      <c r="F18" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="39">
-        <v>24.17</v>
-      </c>
-      <c r="H18" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="39">
-        <v>28.44</v>
-      </c>
-      <c r="J18" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="40">
-        <v>0.16</v>
-      </c>
-      <c r="L18" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="44">
-        <v>3</v>
-      </c>
+      <c r="A18" s="21"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
     </row>
     <row r="19" s="5" customFormat="1" ht="16" customHeight="1" spans="1:81">
       <c r="A19" s="46"/>
@@ -3374,91 +3043,91 @@
     </row>
     <row r="20" ht="16" customHeight="1" spans="1:81">
       <c r="A20" s="53" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
-      <c r="B20" s="25"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="53"/>
       <c r="D20" s="17"/>
-      <c r="E20" s="34">
+      <c r="E20" s="35">
         <f t="shared" ref="E20:I20" si="0">SUM(E10:E19)</f>
-        <v>1277</v>
+        <v>0</v>
       </c>
       <c r="F20" s="54" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="41">
         <f t="shared" si="0"/>
-        <v>851.03</v>
+        <v>0</v>
       </c>
-      <c r="H20" s="56" t="s">
-        <v>25</v>
+      <c r="H20" s="55" t="s">
+        <v>19</v>
       </c>
-      <c r="I20" s="56">
+      <c r="I20" s="55">
         <f t="shared" si="0"/>
-        <v>1001.21</v>
+        <v>0</v>
       </c>
-      <c r="J20" s="56" t="s">
-        <v>25</v>
+      <c r="J20" s="55" t="s">
+        <v>19</v>
       </c>
-      <c r="K20" s="56">
+      <c r="K20" s="55">
         <f>SUM(K10:K19)</f>
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="L20" s="54" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
-      <c r="M20" s="56">
+      <c r="M20" s="55">
         <f>SUM(M10:M19)</f>
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" ht="16" customHeight="1" spans="1:81">
-      <c r="A21" s="57"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="63"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="59"/>
-      <c r="O21" s="64"/>
+      <c r="A21" s="56"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="58"/>
+      <c r="O21" s="63"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="16" customHeight="1" spans="1:81">
-      <c r="A22" s="57"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="59"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="58"/>
     </row>
     <row r="23" s="3" customFormat="1" ht="16" customHeight="1" spans="1:81">
-      <c r="A23" s="65" t="s">
-        <v>36</v>
+      <c r="A23" s="64" t="s">
+        <v>21</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="59"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="56"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="58"/>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
@@ -3527,41 +3196,39 @@
       <c r="CB23" s="4"/>
       <c r="CC23" s="4"/>
     </row>
-    <row r="24" ht="15.5" spans="1:81">
-      <c r="A24" s="65" t="s">
-        <v>37</v>
+    <row r="24" spans="1:81">
+      <c r="A24" s="64" t="s">
+        <v>22</v>
       </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="66" t="s">
-        <v>38</v>
+      <c r="B24" s="57"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="58"/>
+    </row>
+    <row r="25" spans="1:81">
+      <c r="A25" s="64" t="s">
+        <v>23</v>
       </c>
-      <c r="E24" s="60"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="63"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="59"/>
-    </row>
-    <row r="25" ht="15.5" spans="1:81">
-      <c r="A25" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="63"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="59"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="58"/>
     </row>
     <row r="28" spans="1:81">
       <c r="I28" s="7"/>
